--- a/A2259C_C_MARKER.xlsx
+++ b/A2259C_C_MARKER.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myrp-my.sharepoint.com/personal/paul_z_chen_rp_edu_sg/Documents/A2259C/A2295C graded assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="11_6F1BA1203640E93B7C848278167CB456553A4DAA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30CC3201-8B8C-43B7-A8A2-8987C30FE06C}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="11_6F1BA1203640E93B7C848278167CB456553A4DAA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC7E1973-C56A-4F3E-A92C-E3D4B120BDF4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="1" r:id="rId1"/>
-    <sheet name="Data1" sheetId="2" r:id="rId2"/>
-    <sheet name="Data2" sheetId="3" r:id="rId3"/>
-    <sheet name="Data3" sheetId="4" r:id="rId4"/>
-    <sheet name="QA_Data1" sheetId="5" r:id="rId5"/>
-    <sheet name="QA_Data2" sheetId="6" r:id="rId6"/>
+    <sheet name="QA_Data1" sheetId="5" r:id="rId2"/>
+    <sheet name="Data1" sheetId="2" r:id="rId3"/>
+    <sheet name="Data2" sheetId="3" r:id="rId4"/>
+    <sheet name="QA_Data2" sheetId="6" r:id="rId5"/>
+    <sheet name="Data3" sheetId="4" r:id="rId6"/>
     <sheet name="QA_Data3" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -62,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="283">
   <si>
     <t>Outlet_ID</t>
   </si>
@@ -920,6 +919,15 @@
   </si>
   <si>
     <t>Percentile</t>
+  </si>
+  <si>
+    <t>Briefly discuss one limitation of relying on generative AI to solve this question.</t>
+  </si>
+  <si>
+    <t>AI may suggest an incorrect model if context is misunderstood 
+AI may not correctly handle dummy variable creation in Excel 
+AI may give generic interpretations without checking assumptions 
+AI outputs depend on correct user input and may overlook data issues</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1007,13 +1015,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3302,6 +3313,182 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7">
+        <f>AVERAGE(tzdata[Nitrate_mgL])</f>
+        <v>8.7795454545454525</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8">
+        <f>COUNT(tzdata[Nitrate_mgL])</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9">
+        <f>(AVERAGE(tzdata[Nitrate_mgL])-10)/(2.5/SQRT(COUNT(tzdata[Nitrate_mgL])))</f>
+        <v>-3.9660078393541078</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D10">
+        <f>2*(1-_xlfn.NORM.S.DIST(ABS((AVERAGE(tzdata[Nitrate_mgL])-10)/(2.5/SQRT(COUNT(tzdata[Nitrate_mgL])))),TRUE))</f>
+        <v>7.3086459516868985E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(QA_Data1!D10&lt;0.05,"Reject null","Cannot reject null")</f>
+        <v>Reject null</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B67"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3840,441 +4027,6 @@
       </c>
       <c r="B67">
         <v>10.49</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
-  </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2">
-        <v>268.5</v>
-      </c>
-      <c r="C2">
-        <v>233.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3">
-        <v>207.2</v>
-      </c>
-      <c r="C3">
-        <v>189.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4">
-        <v>362</v>
-      </c>
-      <c r="C4">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5">
-        <v>463.7</v>
-      </c>
-      <c r="C5">
-        <v>430.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6">
-        <v>264.60000000000002</v>
-      </c>
-      <c r="C6">
-        <v>243.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7">
-        <v>331.3</v>
-      </c>
-      <c r="C7">
-        <v>311.89999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8">
-        <v>225.4</v>
-      </c>
-      <c r="C8">
-        <v>207.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9">
-        <v>291.39999999999998</v>
-      </c>
-      <c r="C9">
-        <v>262.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10">
-        <v>212.7</v>
-      </c>
-      <c r="C10">
-        <v>197.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11">
-        <v>181.8</v>
-      </c>
-      <c r="C11">
-        <v>164.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12">
-        <v>280.5</v>
-      </c>
-      <c r="C12">
-        <v>248.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13">
-        <v>152.9</v>
-      </c>
-      <c r="C13">
-        <v>120.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14">
-        <v>327.5</v>
-      </c>
-      <c r="C14">
-        <v>308.60000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15">
-        <v>151.19999999999999</v>
-      </c>
-      <c r="C15">
-        <v>119.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16">
-        <v>275.60000000000002</v>
-      </c>
-      <c r="C16">
-        <v>260.60000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17">
-        <v>250</v>
-      </c>
-      <c r="C17">
-        <v>231.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18">
-        <v>240.4</v>
-      </c>
-      <c r="C18">
-        <v>213.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19">
-        <v>375.4</v>
-      </c>
-      <c r="C19">
-        <v>357.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20">
-        <v>329.6</v>
-      </c>
-      <c r="C20">
-        <v>313.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21">
-        <v>269.2</v>
-      </c>
-      <c r="C21">
-        <v>255.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22">
-        <v>186.6</v>
-      </c>
-      <c r="C22">
-        <v>165.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23">
-        <v>244.5</v>
-      </c>
-      <c r="C23">
-        <v>227.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24">
-        <v>238.5</v>
-      </c>
-      <c r="C24">
-        <v>212.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25">
-        <v>174.6</v>
-      </c>
-      <c r="C25">
-        <v>175.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>92</v>
-      </c>
-      <c r="B26">
-        <v>365.2</v>
-      </c>
-      <c r="C26">
-        <v>337.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>93</v>
-      </c>
-      <c r="B27">
-        <v>304.3</v>
-      </c>
-      <c r="C27">
-        <v>299.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>94</v>
-      </c>
-      <c r="B28">
-        <v>178.2</v>
-      </c>
-      <c r="C28">
-        <v>137.1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>95</v>
-      </c>
-      <c r="B29">
-        <v>281.60000000000002</v>
-      </c>
-      <c r="C29">
-        <v>263.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30">
-        <v>251.1</v>
-      </c>
-      <c r="C30">
-        <v>230.1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31">
-        <v>234.1</v>
-      </c>
-      <c r="C31">
-        <v>210.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32">
-        <v>280</v>
-      </c>
-      <c r="C32">
-        <v>242.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33">
-        <v>228.7</v>
-      </c>
-      <c r="C33">
-        <v>221.2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>100</v>
-      </c>
-      <c r="B34">
-        <v>237.6</v>
-      </c>
-      <c r="C34">
-        <v>217.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>101</v>
-      </c>
-      <c r="B35">
-        <v>180.4</v>
-      </c>
-      <c r="C35">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36">
-        <v>340.04244996729301</v>
-      </c>
-      <c r="C36">
-        <v>214.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>103</v>
-      </c>
-      <c r="B37">
-        <v>242.6</v>
-      </c>
-      <c r="C37">
-        <v>241.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>104</v>
-      </c>
-      <c r="B38">
-        <v>302.2</v>
-      </c>
-      <c r="C38">
-        <v>271.3</v>
       </c>
     </row>
   </sheetData>
@@ -4290,6 +4042,609 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2">
+        <v>268.5</v>
+      </c>
+      <c r="C2">
+        <v>233.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3">
+        <v>207.2</v>
+      </c>
+      <c r="C3">
+        <v>189.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4">
+        <v>362</v>
+      </c>
+      <c r="C4">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5">
+        <v>463.7</v>
+      </c>
+      <c r="C5">
+        <v>430.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6">
+        <v>264.60000000000002</v>
+      </c>
+      <c r="C6">
+        <v>243.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7">
+        <v>331.3</v>
+      </c>
+      <c r="C7">
+        <v>311.89999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8">
+        <v>225.4</v>
+      </c>
+      <c r="C8">
+        <v>207.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9">
+        <v>291.39999999999998</v>
+      </c>
+      <c r="C9">
+        <v>262.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10">
+        <v>212.7</v>
+      </c>
+      <c r="C10">
+        <v>197.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11">
+        <v>181.8</v>
+      </c>
+      <c r="C11">
+        <v>164.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12">
+        <v>280.5</v>
+      </c>
+      <c r="C12">
+        <v>248.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13">
+        <v>152.9</v>
+      </c>
+      <c r="C13">
+        <v>120.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14">
+        <v>327.5</v>
+      </c>
+      <c r="C14">
+        <v>308.60000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="C15">
+        <v>119.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16">
+        <v>275.60000000000002</v>
+      </c>
+      <c r="C16">
+        <v>260.60000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17">
+        <v>250</v>
+      </c>
+      <c r="C17">
+        <v>231.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18">
+        <v>240.4</v>
+      </c>
+      <c r="C18">
+        <v>213.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19">
+        <v>375.4</v>
+      </c>
+      <c r="C19">
+        <v>357.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20">
+        <v>329.6</v>
+      </c>
+      <c r="C20">
+        <v>313.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21">
+        <v>269.2</v>
+      </c>
+      <c r="C21">
+        <v>255.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22">
+        <v>186.6</v>
+      </c>
+      <c r="C22">
+        <v>165.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23">
+        <v>244.5</v>
+      </c>
+      <c r="C23">
+        <v>227.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24">
+        <v>238.5</v>
+      </c>
+      <c r="C24">
+        <v>212.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25">
+        <v>174.6</v>
+      </c>
+      <c r="C25">
+        <v>175.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26">
+        <v>365.2</v>
+      </c>
+      <c r="C26">
+        <v>337.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27">
+        <v>304.3</v>
+      </c>
+      <c r="C27">
+        <v>299.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28">
+        <v>178.2</v>
+      </c>
+      <c r="C28">
+        <v>137.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29">
+        <v>281.60000000000002</v>
+      </c>
+      <c r="C29">
+        <v>263.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30">
+        <v>251.1</v>
+      </c>
+      <c r="C30">
+        <v>230.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31">
+        <v>234.1</v>
+      </c>
+      <c r="C31">
+        <v>210.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32">
+        <v>280</v>
+      </c>
+      <c r="C32">
+        <v>242.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33">
+        <v>228.7</v>
+      </c>
+      <c r="C33">
+        <v>221.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34">
+        <v>237.6</v>
+      </c>
+      <c r="C34">
+        <v>217.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35">
+        <v>180.4</v>
+      </c>
+      <c r="C35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36">
+        <v>340.04244996729301</v>
+      </c>
+      <c r="C36">
+        <v>214.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37">
+        <v>242.6</v>
+      </c>
+      <c r="C37">
+        <v>241.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38">
+        <v>302.2</v>
+      </c>
+      <c r="C38">
+        <v>271.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" cm="1">
+        <f t="array" ref="D8">(AVERAGE(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay]))/(_xlfn.STDEV.S(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])/SQRT(COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])))</f>
+        <v>-7.3934524835519122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" cm="1">
+        <f t="array" ref="D9">_xlfn.SINGLE(_xlfn.T.DIST(ABS((AVERAGE(tpairdata[[#This Row],[After_kWhDay]]-tpairdata[Before_kWhDay]))/(_xlfn.STDEV.S(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])/SQRT(COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])))), COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])-1,))</f>
+        <v>0.39438057353125094</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(D9&lt;0.05,"Reject null","Cannot reject null")</f>
+        <v>Cannot reject null</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O96"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4354,10 +4709,10 @@
       <c r="E3">
         <v>33.9</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -4377,10 +4732,10 @@
       <c r="E4">
         <v>41.9</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" t="s">
         <v>253</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>0.15585793912022697</v>
       </c>
     </row>
@@ -4402,10 +4757,10 @@
       <c r="E5">
         <v>44</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" t="s">
         <v>254</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>2.4291697186804379E-2</v>
       </c>
     </row>
@@ -4427,10 +4782,10 @@
       <c r="E6">
         <v>29.7</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" t="s">
         <v>255</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6">
         <v>-4.4056058371131392E-3</v>
       </c>
     </row>
@@ -4452,10 +4807,10 @@
       <c r="E7">
         <v>40.4</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" t="s">
         <v>256</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7">
         <v>7.7834225809858824</v>
       </c>
     </row>
@@ -4477,10 +4832,10 @@
       <c r="E8">
         <v>41.9</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>71</v>
       </c>
     </row>
@@ -4543,20 +4898,20 @@
       <c r="E11">
         <v>52.9</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6" t="s">
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="5" t="s">
         <v>267</v>
       </c>
     </row>
@@ -4578,22 +4933,22 @@
       <c r="E12">
         <v>40</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" t="s">
         <v>259</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12">
         <v>2</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12">
         <v>102.56235649822338</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12">
         <v>51.28117824911169</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12">
         <v>0.84648014367617319</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12">
         <v>0.43339113333611912</v>
       </c>
     </row>
@@ -4615,20 +4970,18 @@
       <c r="E13">
         <v>37</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" t="s">
         <v>260</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13">
         <v>68</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13">
         <v>4119.5533610456632</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13">
         <v>60.581667074200929</v>
       </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -4648,18 +5001,18 @@
       <c r="E14">
         <v>41.1</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>70</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
         <v>4222.1157175438866</v>
       </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -4698,29 +5051,29 @@
       <c r="E16">
         <v>47.4</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6" t="s">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="N16" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="O16" s="6" t="s">
+      <c r="O16" s="5" t="s">
         <v>274</v>
       </c>
     </row>
@@ -4742,31 +5095,31 @@
       <c r="E17">
         <v>35.5</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" t="s">
         <v>262</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17">
         <v>41.990476190476187</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17">
         <v>1.6984820544379202</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17">
         <v>24.722354929073493</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17">
         <v>1.0563383385368451E-35</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17">
         <v>38.601208020254184</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M17">
         <v>45.37974436069819</v>
       </c>
-      <c r="N17" s="4">
+      <c r="N17">
         <v>38.601208020254184</v>
       </c>
-      <c r="O17" s="4">
+      <c r="O17">
         <v>45.37974436069819</v>
       </c>
     </row>
@@ -4788,31 +5141,31 @@
       <c r="E18">
         <v>56.1</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" t="s">
         <v>109</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18">
         <v>2.8100985073529499</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18">
         <v>2.1858678791995723</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18">
         <v>1.2855756443897974</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18">
         <v>0.20295215044686291</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18">
         <v>-1.5517329338002366</v>
       </c>
-      <c r="M18" s="4">
+      <c r="M18">
         <v>7.1719299485061363</v>
       </c>
-      <c r="N18" s="4">
+      <c r="N18">
         <v>-1.5517329338002366</v>
       </c>
-      <c r="O18" s="4">
+      <c r="O18">
         <v>7.1719299485061363</v>
       </c>
     </row>
@@ -4834,31 +5187,31 @@
       <c r="E19">
         <v>34.299999999999997</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>1.2706349206349203</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="4">
         <v>2.5000978900908257</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="4">
         <v>0.50823406782234415</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="4">
         <v>0.61293403514539768</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="4">
         <v>-3.7182327445746228</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="4">
         <v>6.259502585844464</v>
       </c>
-      <c r="N19" s="5">
+      <c r="N19" s="4">
         <v>-3.7182327445746228</v>
       </c>
-      <c r="O19" s="5">
+      <c r="O19" s="4">
         <v>6.259502585844464</v>
       </c>
     </row>
@@ -4981,19 +5334,19 @@
       <c r="E25">
         <v>43.5</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="5" t="s">
         <v>107</v>
       </c>
     </row>
@@ -5015,19 +5368,19 @@
       <c r="E26">
         <v>34.9</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26">
         <v>1</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26">
         <v>44.800574697829134</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26">
         <v>0.39942530217086869</v>
       </c>
-      <c r="K26" s="4">
+      <c r="K26">
         <v>0.70422535211267601</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L26">
         <v>23.1</v>
       </c>
     </row>
@@ -5049,19 +5402,19 @@
       <c r="E27">
         <v>39.6</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27">
         <v>2</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27">
         <v>41.990476190476187</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27">
         <v>-8.0904761904761884</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K27">
         <v>2.112676056338028</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27">
         <v>28.5</v>
       </c>
     </row>
@@ -5083,19 +5436,19 @@
       <c r="E28">
         <v>31.2</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28">
         <v>3</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28">
         <v>43.261111111111106</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I28">
         <v>-1.3611111111111072</v>
       </c>
-      <c r="K28" s="4">
+      <c r="K28">
         <v>3.52112676056338</v>
       </c>
-      <c r="L28" s="4">
+      <c r="L28">
         <v>29.7</v>
       </c>
     </row>
@@ -5117,19 +5470,19 @@
       <c r="E29">
         <v>53.1</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29">
         <v>4</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29">
         <v>44.800574697829134</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29">
         <v>-0.80057469782913415</v>
       </c>
-      <c r="K29" s="4">
+      <c r="K29">
         <v>4.929577464788732</v>
       </c>
-      <c r="L29" s="4">
+      <c r="L29">
         <v>31.2</v>
       </c>
     </row>
@@ -5151,19 +5504,19 @@
       <c r="E30">
         <v>43.4</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30">
         <v>5</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30">
         <v>44.800574697829134</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30">
         <v>-15.100574697829135</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K30">
         <v>6.3380281690140841</v>
       </c>
-      <c r="L30" s="4">
+      <c r="L30">
         <v>33.1</v>
       </c>
     </row>
@@ -5185,19 +5538,19 @@
       <c r="E31">
         <v>44.3</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31">
         <v>6</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31">
         <v>44.800574697829134</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I31">
         <v>-4.4005746978291356</v>
       </c>
-      <c r="K31" s="4">
+      <c r="K31">
         <v>7.7464788732394361</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L31">
         <v>33.6</v>
       </c>
     </row>
@@ -5219,19 +5572,19 @@
       <c r="E32">
         <v>41</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32">
         <v>7</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32">
         <v>44.800574697829134</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32">
         <v>-2.9005746978291356</v>
       </c>
-      <c r="K32" s="4">
+      <c r="K32">
         <v>9.1549295774647881</v>
       </c>
-      <c r="L32" s="4">
+      <c r="L32">
         <v>33.9</v>
       </c>
     </row>
@@ -5253,19 +5606,19 @@
       <c r="E33">
         <v>48.4</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33">
         <v>8</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33">
         <v>43.261111111111106</v>
       </c>
-      <c r="I33" s="4">
+      <c r="I33">
         <v>11.938888888888897</v>
       </c>
-      <c r="K33" s="4">
+      <c r="K33">
         <v>10.56338028169014</v>
       </c>
-      <c r="L33" s="4">
+      <c r="L33">
         <v>34.299999999999997</v>
       </c>
     </row>
@@ -5287,19 +5640,19 @@
       <c r="E34">
         <v>51.5</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34">
         <v>9</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H34">
         <v>41.990476190476187</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I34">
         <v>-3.7904761904761841</v>
       </c>
-      <c r="K34" s="4">
+      <c r="K34">
         <v>11.971830985915492</v>
       </c>
-      <c r="L34" s="4">
+      <c r="L34">
         <v>34.9</v>
       </c>
     </row>
@@ -5321,19 +5674,19 @@
       <c r="E35">
         <v>54.6</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35">
         <v>10</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H35">
         <v>41.990476190476187</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I35">
         <v>10.909523809523812</v>
       </c>
-      <c r="K35" s="4">
+      <c r="K35">
         <v>13.380281690140844</v>
       </c>
-      <c r="L35" s="4">
+      <c r="L35">
         <v>34.9</v>
       </c>
     </row>
@@ -5355,19 +5708,19 @@
       <c r="E36">
         <v>42.6</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36">
         <v>11</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36">
         <v>43.261111111111106</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36">
         <v>-3.2611111111111057</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K36">
         <v>14.788732394366196</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L36">
         <v>35.5</v>
       </c>
     </row>
@@ -5389,19 +5742,19 @@
       <c r="E37">
         <v>42.3</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37">
         <v>12</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H37">
         <v>43.261111111111106</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I37">
         <v>-6.2611111111111057</v>
       </c>
-      <c r="K37" s="4">
+      <c r="K37">
         <v>16.197183098591548</v>
       </c>
-      <c r="L37" s="4">
+      <c r="L37">
         <v>35.700000000000003</v>
       </c>
     </row>
@@ -5423,19 +5776,19 @@
       <c r="E38">
         <v>51.6</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38">
         <v>13</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H38">
         <v>41.990476190476187</v>
       </c>
-      <c r="I38" s="4">
+      <c r="I38">
         <v>-0.89047619047618554</v>
       </c>
-      <c r="K38" s="4">
+      <c r="K38">
         <v>17.6056338028169</v>
       </c>
-      <c r="L38" s="4">
+      <c r="L38">
         <v>36.700000000000003</v>
       </c>
     </row>
@@ -5457,19 +5810,19 @@
       <c r="E39">
         <v>47</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39">
         <v>14</v>
       </c>
-      <c r="H39" s="4">
+      <c r="H39">
         <v>44.800574697829134</v>
       </c>
-      <c r="I39" s="4">
+      <c r="I39">
         <v>1.0994253021708644</v>
       </c>
-      <c r="K39" s="4">
+      <c r="K39">
         <v>19.014084507042252</v>
       </c>
-      <c r="L39" s="4">
+      <c r="L39">
         <v>36.9</v>
       </c>
     </row>
@@ -5491,19 +5844,19 @@
       <c r="E40">
         <v>50.5</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40">
         <v>15</v>
       </c>
-      <c r="H40" s="4">
+      <c r="H40">
         <v>41.990476190476187</v>
       </c>
-      <c r="I40" s="4">
+      <c r="I40">
         <v>5.4095238095238116</v>
       </c>
-      <c r="K40" s="4">
+      <c r="K40">
         <v>20.422535211267604</v>
       </c>
-      <c r="L40" s="4">
+      <c r="L40">
         <v>37</v>
       </c>
     </row>
@@ -5525,19 +5878,19 @@
       <c r="E41">
         <v>69.618390330532606</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41">
         <v>16</v>
       </c>
-      <c r="H41" s="4">
+      <c r="H41">
         <v>43.261111111111106</v>
       </c>
-      <c r="I41" s="4">
+      <c r="I41">
         <v>-7.7611111111111057</v>
       </c>
-      <c r="K41" s="4">
+      <c r="K41">
         <v>21.830985915492956</v>
       </c>
-      <c r="L41" s="4">
+      <c r="L41">
         <v>37.1</v>
       </c>
     </row>
@@ -5559,19 +5912,19 @@
       <c r="E42">
         <v>38.200000000000003</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G42">
         <v>17</v>
       </c>
-      <c r="H42" s="4">
+      <c r="H42">
         <v>44.800574697829134</v>
       </c>
-      <c r="I42" s="4">
+      <c r="I42">
         <v>11.299425302170867</v>
       </c>
-      <c r="K42" s="4">
+      <c r="K42">
         <v>23.239436619718308</v>
       </c>
-      <c r="L42" s="4">
+      <c r="L42">
         <v>38.200000000000003</v>
       </c>
     </row>
@@ -5593,19 +5946,19 @@
       <c r="E43">
         <v>37.1</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43">
         <v>18</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H43">
         <v>43.261111111111106</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I43">
         <v>-8.9611111111111086</v>
       </c>
-      <c r="K43" s="4">
+      <c r="K43">
         <v>24.64788732394366</v>
       </c>
-      <c r="L43" s="4">
+      <c r="L43">
         <v>38.200000000000003</v>
       </c>
     </row>
@@ -5627,19 +5980,19 @@
       <c r="E44">
         <v>51.9</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44">
         <v>19</v>
       </c>
-      <c r="H44" s="4">
+      <c r="H44">
         <v>44.800574697829134</v>
       </c>
-      <c r="I44" s="4">
+      <c r="I44">
         <v>-16.300574697829134</v>
       </c>
-      <c r="K44" s="4">
+      <c r="K44">
         <v>26.056338028169012</v>
       </c>
-      <c r="L44" s="4">
+      <c r="L44">
         <v>39.4</v>
       </c>
     </row>
@@ -5661,19 +6014,19 @@
       <c r="E45">
         <v>42.6</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45">
         <v>20</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H45">
         <v>41.990476190476187</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I45">
         <v>1.009523809523813</v>
       </c>
-      <c r="K45" s="4">
+      <c r="K45">
         <v>27.464788732394364</v>
       </c>
-      <c r="L45" s="4">
+      <c r="L45">
         <v>39.6</v>
       </c>
     </row>
@@ -5695,19 +6048,19 @@
       <c r="E46">
         <v>46.6</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46">
         <v>21</v>
       </c>
-      <c r="H46" s="4">
+      <c r="H46">
         <v>44.800574697829134</v>
       </c>
-      <c r="I46" s="4">
+      <c r="I46">
         <v>7.499425302170863</v>
       </c>
-      <c r="K46" s="4">
+      <c r="K46">
         <v>28.873239436619716</v>
       </c>
-      <c r="L46" s="4">
+      <c r="L46">
         <v>40</v>
       </c>
     </row>
@@ -5729,19 +6082,19 @@
       <c r="E47">
         <v>40.9</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G47">
         <v>22</v>
       </c>
-      <c r="H47" s="4">
+      <c r="H47">
         <v>43.261111111111106</v>
       </c>
-      <c r="I47" s="4">
+      <c r="I47">
         <v>3.3388888888888957</v>
       </c>
-      <c r="K47" s="4">
+      <c r="K47">
         <v>30.281690140845068</v>
       </c>
-      <c r="L47" s="4">
+      <c r="L47">
         <v>40.200000000000003</v>
       </c>
     </row>
@@ -5763,19 +6116,19 @@
       <c r="E48">
         <v>23.1</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G48">
         <v>23</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H48">
         <v>41.990476190476187</v>
       </c>
-      <c r="I48" s="4">
+      <c r="I48">
         <v>3.6095238095238145</v>
       </c>
-      <c r="K48" s="4">
+      <c r="K48">
         <v>31.69014084507042</v>
       </c>
-      <c r="L48" s="4">
+      <c r="L48">
         <v>40.4</v>
       </c>
     </row>
@@ -5797,19 +6150,19 @@
       <c r="E49">
         <v>35.700000000000003</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G49">
         <v>24</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H49">
         <v>44.800574697829134</v>
       </c>
-      <c r="I49" s="4">
+      <c r="I49">
         <v>-1.3005746978291342</v>
       </c>
-      <c r="K49" s="4">
+      <c r="K49">
         <v>33.098591549295776</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L49">
         <v>40.5</v>
       </c>
     </row>
@@ -5831,19 +6184,19 @@
       <c r="E50">
         <v>50.8</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G50">
         <v>25</v>
       </c>
-      <c r="H50" s="4">
+      <c r="H50">
         <v>44.800574697829134</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I50">
         <v>-9.9005746978291356</v>
       </c>
-      <c r="K50" s="4">
+      <c r="K50">
         <v>34.507042253521121</v>
       </c>
-      <c r="L50" s="4">
+      <c r="L50">
         <v>40.9</v>
       </c>
     </row>
@@ -5865,19 +6218,19 @@
       <c r="E51">
         <v>43.2</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G51">
         <v>26</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H51">
         <v>41.990476190476187</v>
       </c>
-      <c r="I51" s="4">
+      <c r="I51">
         <v>-2.3904761904761855</v>
       </c>
-      <c r="K51" s="4">
+      <c r="K51">
         <v>35.91549295774648</v>
       </c>
-      <c r="L51" s="4">
+      <c r="L51">
         <v>41</v>
       </c>
     </row>
@@ -5899,19 +6252,19 @@
       <c r="E52">
         <v>36.700000000000003</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G52">
         <v>27</v>
       </c>
-      <c r="H52" s="4">
+      <c r="H52">
         <v>41.990476190476187</v>
       </c>
-      <c r="I52" s="4">
+      <c r="I52">
         <v>-10.790476190476188</v>
       </c>
-      <c r="K52" s="4">
+      <c r="K52">
         <v>37.323943661971825</v>
       </c>
-      <c r="L52" s="4">
+      <c r="L52">
         <v>41.1</v>
       </c>
     </row>
@@ -5933,19 +6286,19 @@
       <c r="E53">
         <v>48.5</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G53">
         <v>28</v>
       </c>
-      <c r="H53" s="4">
+      <c r="H53">
         <v>44.800574697829134</v>
       </c>
-      <c r="I53" s="4">
+      <c r="I53">
         <v>8.2994253021708673</v>
       </c>
-      <c r="K53" s="4">
+      <c r="K53">
         <v>38.732394366197184</v>
       </c>
-      <c r="L53" s="4">
+      <c r="L53">
         <v>41.8</v>
       </c>
     </row>
@@ -5967,19 +6320,19 @@
       <c r="E54">
         <v>54.2</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G54">
         <v>29</v>
       </c>
-      <c r="H54" s="4">
+      <c r="H54">
         <v>41.990476190476187</v>
       </c>
-      <c r="I54" s="4">
+      <c r="I54">
         <v>1.4095238095238116</v>
       </c>
-      <c r="K54" s="4">
+      <c r="K54">
         <v>40.140845070422529</v>
       </c>
-      <c r="L54" s="4">
+      <c r="L54">
         <v>41.9</v>
       </c>
     </row>
@@ -6001,19 +6354,19 @@
       <c r="E55">
         <v>44.9</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G55">
         <v>30</v>
       </c>
-      <c r="H55" s="4">
+      <c r="H55">
         <v>41.990476190476187</v>
       </c>
-      <c r="I55" s="4">
+      <c r="I55">
         <v>2.3095238095238102</v>
       </c>
-      <c r="K55" s="4">
+      <c r="K55">
         <v>41.549295774647888</v>
       </c>
-      <c r="L55" s="4">
+      <c r="L55">
         <v>41.9</v>
       </c>
     </row>
@@ -6035,19 +6388,19 @@
       <c r="E56">
         <v>36.9</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G56">
         <v>31</v>
       </c>
-      <c r="H56" s="4">
+      <c r="H56">
         <v>44.800574697829134</v>
       </c>
-      <c r="I56" s="4">
+      <c r="I56">
         <v>-3.8005746978291342</v>
       </c>
-      <c r="K56" s="4">
+      <c r="K56">
         <v>42.957746478873233</v>
       </c>
-      <c r="L56" s="4">
+      <c r="L56">
         <v>42.1</v>
       </c>
     </row>
@@ -6069,19 +6422,19 @@
       <c r="E57">
         <v>46.3</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G57">
         <v>32</v>
       </c>
-      <c r="H57" s="4">
+      <c r="H57">
         <v>44.800574697829134</v>
       </c>
-      <c r="I57" s="4">
+      <c r="I57">
         <v>3.5994253021708644</v>
       </c>
-      <c r="K57" s="4">
+      <c r="K57">
         <v>44.366197183098592</v>
       </c>
-      <c r="L57" s="4">
+      <c r="L57">
         <v>42.3</v>
       </c>
     </row>
@@ -6103,19 +6456,19 @@
       <c r="E58">
         <v>39.4</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G58">
         <v>33</v>
       </c>
-      <c r="H58" s="4">
+      <c r="H58">
         <v>44.800574697829134</v>
       </c>
-      <c r="I58" s="4">
+      <c r="I58">
         <v>6.6994253021708658</v>
       </c>
-      <c r="K58" s="4">
+      <c r="K58">
         <v>45.774647887323937</v>
       </c>
-      <c r="L58" s="4">
+      <c r="L58">
         <v>42.4</v>
       </c>
     </row>
@@ -6137,19 +6490,19 @@
       <c r="E59">
         <v>52.1</v>
       </c>
-      <c r="G59" s="4">
+      <c r="G59">
         <v>34</v>
       </c>
-      <c r="H59" s="4">
+      <c r="H59">
         <v>43.261111111111106</v>
       </c>
-      <c r="I59" s="4">
+      <c r="I59">
         <v>11.338888888888896</v>
       </c>
-      <c r="K59" s="4">
+      <c r="K59">
         <v>47.183098591549296</v>
       </c>
-      <c r="L59" s="4">
+      <c r="L59">
         <v>42.6</v>
       </c>
     </row>
@@ -6171,19 +6524,19 @@
       <c r="E60">
         <v>34.9</v>
       </c>
-      <c r="G60" s="4">
+      <c r="G60">
         <v>35</v>
       </c>
-      <c r="H60" s="4">
+      <c r="H60">
         <v>41.990476190476187</v>
       </c>
-      <c r="I60" s="4">
+      <c r="I60">
         <v>0.60952380952381446</v>
       </c>
-      <c r="K60" s="4">
+      <c r="K60">
         <v>48.591549295774641</v>
       </c>
-      <c r="L60" s="4">
+      <c r="L60">
         <v>42.6</v>
       </c>
     </row>
@@ -6205,19 +6558,19 @@
       <c r="E61">
         <v>53.4</v>
       </c>
-      <c r="G61" s="4">
+      <c r="G61">
         <v>36</v>
       </c>
-      <c r="H61" s="4">
+      <c r="H61">
         <v>44.800574697829134</v>
       </c>
-      <c r="I61" s="4">
+      <c r="I61">
         <v>-2.500574697829137</v>
       </c>
-      <c r="K61" s="4">
+      <c r="K61">
         <v>50</v>
       </c>
-      <c r="L61" s="4">
+      <c r="L61">
         <v>43</v>
       </c>
     </row>
@@ -6239,19 +6592,19 @@
       <c r="E62">
         <v>42.4</v>
       </c>
-      <c r="G62" s="4">
+      <c r="G62">
         <v>37</v>
       </c>
-      <c r="H62" s="4">
+      <c r="H62">
         <v>43.261111111111106</v>
       </c>
-      <c r="I62" s="4">
+      <c r="I62">
         <v>8.3388888888888957</v>
       </c>
-      <c r="K62" s="4">
+      <c r="K62">
         <v>51.408450704225345</v>
       </c>
-      <c r="L62" s="4">
+      <c r="L62">
         <v>43.2</v>
       </c>
     </row>
@@ -6273,19 +6626,19 @@
       <c r="E63">
         <v>51</v>
       </c>
-      <c r="G63" s="4">
+      <c r="G63">
         <v>38</v>
       </c>
-      <c r="H63" s="4">
+      <c r="H63">
         <v>44.800574697829134</v>
       </c>
-      <c r="I63" s="4">
+      <c r="I63">
         <v>2.1994253021708658</v>
       </c>
-      <c r="K63" s="4">
+      <c r="K63">
         <v>52.816901408450704</v>
       </c>
-      <c r="L63" s="4">
+      <c r="L63">
         <v>43.4</v>
       </c>
     </row>
@@ -6307,19 +6660,19 @@
       <c r="E64">
         <v>41.8</v>
       </c>
-      <c r="G64" s="4">
+      <c r="G64">
         <v>39</v>
       </c>
-      <c r="H64" s="4">
+      <c r="H64">
         <v>44.800574697829134</v>
       </c>
-      <c r="I64" s="4">
+      <c r="I64">
         <v>5.6994253021708658</v>
       </c>
-      <c r="K64" s="4">
+      <c r="K64">
         <v>54.225352112676049</v>
       </c>
-      <c r="L64" s="4">
+      <c r="L64">
         <v>43.5</v>
       </c>
     </row>
@@ -6341,19 +6694,19 @@
       <c r="E65">
         <v>42.1</v>
       </c>
-      <c r="G65" s="4">
+      <c r="G65">
         <v>40</v>
       </c>
-      <c r="H65" s="4">
+      <c r="H65">
         <v>44.800574697829134</v>
       </c>
-      <c r="I65" s="4">
+      <c r="I65">
         <v>24.817815632703471</v>
       </c>
-      <c r="K65" s="4">
+      <c r="K65">
         <v>55.633802816901408</v>
       </c>
-      <c r="L65" s="4">
+      <c r="L65">
         <v>44</v>
       </c>
     </row>
@@ -6375,19 +6728,19 @@
       <c r="E66">
         <v>40.200000000000003</v>
       </c>
-      <c r="G66" s="4">
+      <c r="G66">
         <v>41</v>
       </c>
-      <c r="H66" s="4">
+      <c r="H66">
         <v>43.261111111111106</v>
       </c>
-      <c r="I66" s="4">
+      <c r="I66">
         <v>-5.0611111111111029</v>
       </c>
-      <c r="K66" s="4">
+      <c r="K66">
         <v>57.042253521126753</v>
       </c>
-      <c r="L66" s="4">
+      <c r="L66">
         <v>44.3</v>
       </c>
     </row>
@@ -6409,19 +6762,19 @@
       <c r="E67">
         <v>47</v>
       </c>
-      <c r="G67" s="4">
+      <c r="G67">
         <v>42</v>
       </c>
-      <c r="H67" s="4">
+      <c r="H67">
         <v>41.990476190476187</v>
       </c>
-      <c r="I67" s="4">
+      <c r="I67">
         <v>-4.8904761904761855</v>
       </c>
-      <c r="K67" s="4">
+      <c r="K67">
         <v>58.450704225352112</v>
       </c>
-      <c r="L67" s="4">
+      <c r="L67">
         <v>44.9</v>
       </c>
     </row>
@@ -6443,19 +6796,19 @@
       <c r="E68">
         <v>33.6</v>
       </c>
-      <c r="G68" s="4">
+      <c r="G68">
         <v>43</v>
       </c>
-      <c r="H68" s="4">
+      <c r="H68">
         <v>44.800574697829134</v>
       </c>
-      <c r="I68" s="4">
+      <c r="I68">
         <v>7.0994253021708644</v>
       </c>
-      <c r="K68" s="4">
+      <c r="K68">
         <v>59.859154929577457</v>
       </c>
-      <c r="L68" s="4">
+      <c r="L68">
         <v>45.2</v>
       </c>
     </row>
@@ -6477,19 +6830,19 @@
       <c r="E69">
         <v>40.5</v>
       </c>
-      <c r="G69" s="4">
+      <c r="G69">
         <v>44</v>
       </c>
-      <c r="H69" s="4">
+      <c r="H69">
         <v>43.261111111111106</v>
       </c>
-      <c r="I69" s="4">
+      <c r="I69">
         <v>-0.66111111111110432</v>
       </c>
-      <c r="K69" s="4">
+      <c r="K69">
         <v>61.267605633802816</v>
       </c>
-      <c r="L69" s="4">
+      <c r="L69">
         <v>45.4</v>
       </c>
     </row>
@@ -6511,19 +6864,19 @@
       <c r="E70">
         <v>45.4</v>
       </c>
-      <c r="G70" s="4">
+      <c r="G70">
         <v>45</v>
       </c>
-      <c r="H70" s="4">
+      <c r="H70">
         <v>41.990476190476187</v>
       </c>
-      <c r="I70" s="4">
+      <c r="I70">
         <v>4.6095238095238145</v>
       </c>
-      <c r="K70" s="4">
+      <c r="K70">
         <v>62.676056338028161</v>
       </c>
-      <c r="L70" s="4">
+      <c r="L70">
         <v>45.6</v>
       </c>
     </row>
@@ -6545,19 +6898,19 @@
       <c r="E71">
         <v>53.9</v>
       </c>
-      <c r="G71" s="4">
+      <c r="G71">
         <v>46</v>
       </c>
-      <c r="H71" s="4">
+      <c r="H71">
         <v>44.800574697829134</v>
       </c>
-      <c r="I71" s="4">
+      <c r="I71">
         <v>-3.9005746978291356</v>
       </c>
-      <c r="K71" s="4">
+      <c r="K71">
         <v>64.08450704225352</v>
       </c>
-      <c r="L71" s="4">
+      <c r="L71">
         <v>45.9</v>
       </c>
     </row>
@@ -6579,427 +6932,427 @@
       <c r="E72">
         <v>33.1</v>
       </c>
-      <c r="G72" s="4">
+      <c r="G72">
         <v>47</v>
       </c>
-      <c r="H72" s="4">
+      <c r="H72">
         <v>44.800574697829134</v>
       </c>
-      <c r="I72" s="4">
+      <c r="I72">
         <v>-21.700574697829133</v>
       </c>
-      <c r="K72" s="4">
+      <c r="K72">
         <v>65.492957746478865</v>
       </c>
-      <c r="L72" s="4">
+      <c r="L72">
         <v>46.3</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G73" s="4">
+      <c r="G73">
         <v>48</v>
       </c>
-      <c r="H73" s="4">
+      <c r="H73">
         <v>41.990476190476187</v>
       </c>
-      <c r="I73" s="4">
+      <c r="I73">
         <v>-6.2904761904761841</v>
       </c>
-      <c r="K73" s="4">
+      <c r="K73">
         <v>66.901408450704224</v>
       </c>
-      <c r="L73" s="4">
+      <c r="L73">
         <v>46.6</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G74" s="4">
+      <c r="G74">
         <v>49</v>
       </c>
-      <c r="H74" s="4">
+      <c r="H74">
         <v>44.800574697829134</v>
       </c>
-      <c r="I74" s="4">
+      <c r="I74">
         <v>5.999425302170863</v>
       </c>
-      <c r="K74" s="4">
+      <c r="K74">
         <v>68.309859154929569</v>
       </c>
-      <c r="L74" s="4">
+      <c r="L74">
         <v>46.6</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G75" s="4">
+      <c r="G75">
         <v>50</v>
       </c>
-      <c r="H75" s="4">
+      <c r="H75">
         <v>44.800574697829134</v>
       </c>
-      <c r="I75" s="4">
+      <c r="I75">
         <v>-1.6005746978291313</v>
       </c>
-      <c r="K75" s="4">
+      <c r="K75">
         <v>69.718309859154914</v>
       </c>
-      <c r="L75" s="4">
+      <c r="L75">
         <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G76" s="4">
+      <c r="G76">
         <v>51</v>
       </c>
-      <c r="H76" s="4">
+      <c r="H76">
         <v>43.261111111111106</v>
       </c>
-      <c r="I76" s="4">
+      <c r="I76">
         <v>-6.5611111111111029</v>
       </c>
-      <c r="K76" s="4">
+      <c r="K76">
         <v>71.126760563380273</v>
       </c>
-      <c r="L76" s="4">
+      <c r="L76">
         <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G77" s="4">
+      <c r="G77">
         <v>52</v>
       </c>
-      <c r="H77" s="4">
+      <c r="H77">
         <v>44.800574697829134</v>
       </c>
-      <c r="I77" s="4">
+      <c r="I77">
         <v>3.6994253021708658</v>
       </c>
-      <c r="K77" s="4">
+      <c r="K77">
         <v>72.535211267605632</v>
       </c>
-      <c r="L77" s="4">
+      <c r="L77">
         <v>47.4</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G78" s="4">
+      <c r="G78">
         <v>53</v>
       </c>
-      <c r="H78" s="4">
+      <c r="H78">
         <v>44.800574697829134</v>
       </c>
-      <c r="I78" s="4">
+      <c r="I78">
         <v>9.3994253021708687</v>
       </c>
-      <c r="K78" s="4">
+      <c r="K78">
         <v>73.943661971830977</v>
       </c>
-      <c r="L78" s="4">
+      <c r="L78">
         <v>48.4</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G79" s="4">
+      <c r="G79">
         <v>54</v>
       </c>
-      <c r="H79" s="4">
+      <c r="H79">
         <v>44.800574697829134</v>
       </c>
-      <c r="I79" s="4">
+      <c r="I79">
         <v>9.9425302170864427E-2</v>
       </c>
-      <c r="K79" s="4">
+      <c r="K79">
         <v>75.352112676056322</v>
       </c>
-      <c r="L79" s="4">
+      <c r="L79">
         <v>48.5</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G80" s="4">
+      <c r="G80">
         <v>55</v>
       </c>
-      <c r="H80" s="4">
+      <c r="H80">
         <v>43.261111111111106</v>
       </c>
-      <c r="I80" s="4">
+      <c r="I80">
         <v>-6.3611111111111072</v>
       </c>
-      <c r="K80" s="4">
+      <c r="K80">
         <v>76.760563380281681</v>
       </c>
-      <c r="L80" s="4">
+      <c r="L80">
         <v>50.5</v>
       </c>
     </row>
     <row r="81" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G81" s="4">
+      <c r="G81">
         <v>56</v>
       </c>
-      <c r="H81" s="4">
+      <c r="H81">
         <v>44.800574697829134</v>
       </c>
-      <c r="I81" s="4">
+      <c r="I81">
         <v>1.499425302170863</v>
       </c>
-      <c r="K81" s="4">
+      <c r="K81">
         <v>78.16901408450704</v>
       </c>
-      <c r="L81" s="4">
+      <c r="L81">
         <v>50.8</v>
       </c>
     </row>
     <row r="82" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G82" s="4">
+      <c r="G82">
         <v>57</v>
       </c>
-      <c r="H82" s="4">
+      <c r="H82">
         <v>41.990476190476187</v>
       </c>
-      <c r="I82" s="4">
+      <c r="I82">
         <v>-2.5904761904761884</v>
       </c>
-      <c r="K82" s="4">
+      <c r="K82">
         <v>79.577464788732385</v>
       </c>
-      <c r="L82" s="4">
+      <c r="L82">
         <v>51</v>
       </c>
     </row>
     <row r="83" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G83" s="4">
+      <c r="G83">
         <v>58</v>
       </c>
-      <c r="H83" s="4">
+      <c r="H83">
         <v>41.990476190476187</v>
       </c>
-      <c r="I83" s="4">
+      <c r="I83">
         <v>10.109523809523814</v>
       </c>
-      <c r="K83" s="4">
+      <c r="K83">
         <v>80.98591549295773</v>
       </c>
-      <c r="L83" s="4">
+      <c r="L83">
         <v>51.5</v>
       </c>
     </row>
     <row r="84" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G84" s="4">
+      <c r="G84">
         <v>59</v>
       </c>
-      <c r="H84" s="4">
+      <c r="H84">
         <v>44.800574697829134</v>
       </c>
-      <c r="I84" s="4">
+      <c r="I84">
         <v>-9.9005746978291356</v>
       </c>
-      <c r="K84" s="4">
+      <c r="K84">
         <v>82.394366197183089</v>
       </c>
-      <c r="L84" s="4">
+      <c r="L84">
         <v>51.6</v>
       </c>
     </row>
     <row r="85" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G85" s="4">
+      <c r="G85">
         <v>60</v>
       </c>
-      <c r="H85" s="4">
+      <c r="H85">
         <v>41.990476190476187</v>
       </c>
-      <c r="I85" s="4">
+      <c r="I85">
         <v>11.409523809523812</v>
       </c>
-      <c r="K85" s="4">
+      <c r="K85">
         <v>83.802816901408448</v>
       </c>
-      <c r="L85" s="4">
+      <c r="L85">
         <v>51.9</v>
       </c>
     </row>
     <row r="86" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G86" s="4">
+      <c r="G86">
         <v>61</v>
       </c>
-      <c r="H86" s="4">
+      <c r="H86">
         <v>43.261111111111106</v>
       </c>
-      <c r="I86" s="4">
+      <c r="I86">
         <v>-0.86111111111110716</v>
       </c>
-      <c r="K86" s="4">
+      <c r="K86">
         <v>85.211267605633793</v>
       </c>
-      <c r="L86" s="4">
+      <c r="L86">
         <v>52.1</v>
       </c>
     </row>
     <row r="87" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G87" s="4">
+      <c r="G87">
         <v>62</v>
       </c>
-      <c r="H87" s="4">
+      <c r="H87">
         <v>43.261111111111106</v>
       </c>
-      <c r="I87" s="4">
+      <c r="I87">
         <v>7.7388888888888943</v>
       </c>
-      <c r="K87" s="4">
+      <c r="K87">
         <v>86.619718309859138</v>
       </c>
-      <c r="L87" s="4">
+      <c r="L87">
         <v>52.3</v>
       </c>
     </row>
     <row r="88" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G88" s="4">
+      <c r="G88">
         <v>63</v>
       </c>
-      <c r="H88" s="4">
+      <c r="H88">
         <v>43.261111111111106</v>
       </c>
-      <c r="I88" s="4">
+      <c r="I88">
         <v>-1.4611111111111086</v>
       </c>
-      <c r="K88" s="4">
+      <c r="K88">
         <v>88.028169014084497</v>
       </c>
-      <c r="L88" s="4">
+      <c r="L88">
         <v>52.9</v>
       </c>
     </row>
     <row r="89" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G89" s="4">
+      <c r="G89">
         <v>64</v>
       </c>
-      <c r="H89" s="4">
+      <c r="H89">
         <v>44.800574697829134</v>
       </c>
-      <c r="I89" s="4">
+      <c r="I89">
         <v>-2.7005746978291327</v>
       </c>
-      <c r="K89" s="4">
+      <c r="K89">
         <v>89.436619718309856</v>
       </c>
-      <c r="L89" s="4">
+      <c r="L89">
         <v>53.1</v>
       </c>
     </row>
     <row r="90" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G90" s="4">
+      <c r="G90">
         <v>65</v>
       </c>
-      <c r="H90" s="4">
+      <c r="H90">
         <v>41.990476190476187</v>
       </c>
-      <c r="I90" s="4">
+      <c r="I90">
         <v>-1.7904761904761841</v>
       </c>
-      <c r="K90" s="4">
+      <c r="K90">
         <v>90.845070422535201</v>
       </c>
-      <c r="L90" s="4">
+      <c r="L90">
         <v>53.4</v>
       </c>
     </row>
     <row r="91" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G91" s="4">
+      <c r="G91">
         <v>66</v>
       </c>
-      <c r="H91" s="4">
+      <c r="H91">
         <v>43.261111111111106</v>
       </c>
-      <c r="I91" s="4">
+      <c r="I91">
         <v>3.7388888888888943</v>
       </c>
-      <c r="K91" s="4">
+      <c r="K91">
         <v>92.253521126760546</v>
       </c>
-      <c r="L91" s="4">
+      <c r="L91">
         <v>53.9</v>
       </c>
     </row>
     <row r="92" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G92" s="4">
+      <c r="G92">
         <v>67</v>
       </c>
-      <c r="H92" s="4">
+      <c r="H92">
         <v>41.990476190476187</v>
       </c>
-      <c r="I92" s="4">
+      <c r="I92">
         <v>-8.3904761904761855</v>
       </c>
-      <c r="K92" s="4">
+      <c r="K92">
         <v>93.661971830985905</v>
       </c>
-      <c r="L92" s="4">
+      <c r="L92">
         <v>54.2</v>
       </c>
     </row>
     <row r="93" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G93" s="4">
+      <c r="G93">
         <v>68</v>
       </c>
-      <c r="H93" s="4">
+      <c r="H93">
         <v>41.990476190476187</v>
       </c>
-      <c r="I93" s="4">
+      <c r="I93">
         <v>-1.490476190476187</v>
       </c>
-      <c r="K93" s="4">
+      <c r="K93">
         <v>95.070422535211264</v>
       </c>
-      <c r="L93" s="4">
+      <c r="L93">
         <v>54.6</v>
       </c>
     </row>
     <row r="94" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G94" s="4">
+      <c r="G94">
         <v>69</v>
       </c>
-      <c r="H94" s="4">
+      <c r="H94">
         <v>43.261111111111106</v>
       </c>
-      <c r="I94" s="4">
+      <c r="I94">
         <v>2.1388888888888928</v>
       </c>
-      <c r="K94" s="4">
+      <c r="K94">
         <v>96.478873239436609</v>
       </c>
-      <c r="L94" s="4">
+      <c r="L94">
         <v>55.2</v>
       </c>
     </row>
     <row r="95" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G95" s="4">
+      <c r="G95">
         <v>70</v>
       </c>
-      <c r="H95" s="4">
+      <c r="H95">
         <v>44.800574697829134</v>
       </c>
-      <c r="I95" s="4">
+      <c r="I95">
         <v>9.0994253021708644</v>
       </c>
-      <c r="K95" s="4">
+      <c r="K95">
         <v>97.887323943661954</v>
       </c>
-      <c r="L95" s="4">
+      <c r="L95">
         <v>56.1</v>
       </c>
     </row>
     <row r="96" spans="7:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G96" s="5">
+      <c r="G96" s="4">
         <v>71</v>
       </c>
-      <c r="H96" s="5">
+      <c r="H96" s="4">
         <v>44.800574697829134</v>
       </c>
-      <c r="I96" s="5">
+      <c r="I96" s="4">
         <v>-11.700574697829133</v>
       </c>
-      <c r="K96" s="5">
+      <c r="K96" s="4">
         <v>99.295774647887313</v>
       </c>
-      <c r="L96" s="5">
+      <c r="L96" s="4">
         <v>69.618390330532606</v>
       </c>
     </row>
@@ -7019,525 +7372,195 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D11"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="51.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D2" t="s">
-        <v>200</v>
+      <c r="D2" s="7" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D3" t="s">
-        <v>201</v>
+      <c r="D3" s="7" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D7">
-        <f>AVERAGE(tzdata[Nitrate_mgL])</f>
-        <v>8.7795454545454525</v>
+      <c r="D7" s="7" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8">
-        <f>COUNT(tzdata[Nitrate_mgL])</f>
-        <v>66</v>
+      <c r="B8" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9">
-        <f>(AVERAGE(tzdata[Nitrate_mgL])-10)/(2.5/SQRT(COUNT(tzdata[Nitrate_mgL])))</f>
-        <v>-3.9660078393541078</v>
+      <c r="B9" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D10">
-        <f>2*(1-_xlfn.NORM.S.DIST(ABS((AVERAGE(tzdata[Nitrate_mgL])-10)/(2.5/SQRT(COUNT(tzdata[Nitrate_mgL])))),TRUE))</f>
-        <v>7.3086459516868985E-5</v>
+      <c r="B10" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.2706349206349203</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D11" t="str">
-        <f>IF(QA_Data1!D10&lt;0.05,"Reject null","Cannot reject null")</f>
-        <v>Reject null</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B11" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C8" t="s">
-        <v>213</v>
-      </c>
-      <c r="D8" cm="1">
-        <f t="array" ref="D8">(AVERAGE(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay]))/(_xlfn.STDEV.S(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])/SQRT(COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])))</f>
-        <v>-7.3934524835519122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>198</v>
-      </c>
-      <c r="C9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D9" cm="1">
-        <f t="array" ref="D9">_xlfn.SINGLE(_xlfn.T.DIST(ABS((AVERAGE(tpairdata[[#This Row],[After_kWhDay]]-tpairdata[Before_kWhDay]))/(_xlfn.STDEV.S(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])/SQRT(COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])))), COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])-1,))</f>
-        <v>0.39438057353125094</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D11" t="str">
-        <f>IF(D9&lt;0.05,"Reject null","Cannot reject null")</f>
-        <v>Cannot reject null</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="81.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>226</v>
-      </c>
-      <c r="C6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>229</v>
-      </c>
-      <c r="C9" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10">
-        <v>1.2706349206349203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>231</v>
-      </c>
-      <c r="C11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11">
+      <c r="D11" s="7">
         <v>-4.4056058371131392E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="7" t="str">
         <f>IF(Data3!L12&lt;0.05,"Reject null","Cannot reject null")</f>
         <v>Cannot reject null</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="8" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
